--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O528"/>
+  <dimension ref="A1:O530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27354,6 +27354,108 @@
       <c r="O528" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>466.14</v>
+      </c>
+      <c r="C529" t="n">
+        <v>461.54</v>
+      </c>
+      <c r="D529" t="n">
+        <v>455.82</v>
+      </c>
+      <c r="E529" t="n">
+        <v>452.44</v>
+      </c>
+      <c r="F529" t="n">
+        <v>444.85</v>
+      </c>
+      <c r="G529" t="n">
+        <v>443.13</v>
+      </c>
+      <c r="H529" t="n">
+        <v>435.97</v>
+      </c>
+      <c r="I529" t="n">
+        <v>421.81</v>
+      </c>
+      <c r="J529" t="n">
+        <v>417.29</v>
+      </c>
+      <c r="K529" t="n">
+        <v>412.74</v>
+      </c>
+      <c r="L529" t="n">
+        <v>419</v>
+      </c>
+      <c r="M529" t="n">
+        <v>421.88</v>
+      </c>
+      <c r="N529" t="n">
+        <v>423.71</v>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="C530" t="n">
+        <v>460.9</v>
+      </c>
+      <c r="D530" t="n">
+        <v>455.49</v>
+      </c>
+      <c r="E530" t="n">
+        <v>453</v>
+      </c>
+      <c r="F530" t="n">
+        <v>444.87</v>
+      </c>
+      <c r="G530" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="H530" t="n">
+        <v>437.79</v>
+      </c>
+      <c r="I530" t="n">
+        <v>426.75</v>
+      </c>
+      <c r="J530" t="n">
+        <v>423.97</v>
+      </c>
+      <c r="K530" t="n">
+        <v>419.73</v>
+      </c>
+      <c r="L530" t="n">
+        <v>423.71</v>
+      </c>
+      <c r="M530" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="N530" t="n">
+        <v>421.63</v>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27368,7 +27470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32911,6 +33013,26 @@
       </c>
       <c r="B554" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -33079,28 +33201,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.232243665307376</v>
+        <v>2.254538063962396</v>
       </c>
       <c r="J2" t="n">
+        <v>529</v>
+      </c>
+      <c r="K2" t="n">
         <v>527</v>
       </c>
-      <c r="K2" t="n">
-        <v>525</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.6723203207811176</v>
+        <v>0.6733853761454236</v>
       </c>
       <c r="M2" t="n">
-        <v>9.24397069395059</v>
+        <v>9.330328015339695</v>
       </c>
       <c r="N2" t="n">
-        <v>139.7970072621221</v>
+        <v>142.5969145497725</v>
       </c>
       <c r="O2" t="n">
-        <v>11.82357844572116</v>
+        <v>11.94139500015691</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6662120965244</v>
+        <v>376.4342834863386</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33157,28 +33279,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.280396307176385</v>
+        <v>2.303762029489229</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6919042629539267</v>
+        <v>0.6922844677078065</v>
       </c>
       <c r="M3" t="n">
-        <v>9.105309766338667</v>
+        <v>9.208723242100831</v>
       </c>
       <c r="N3" t="n">
-        <v>133.6183269935499</v>
+        <v>136.7818733640964</v>
       </c>
       <c r="O3" t="n">
-        <v>11.55933938395918</v>
+        <v>11.69537829076496</v>
       </c>
       <c r="P3" t="n">
-        <v>368.6137533823451</v>
+        <v>368.3712593130381</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33235,28 +33357,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.138563856499648</v>
+        <v>2.161785720963864</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6703632248652109</v>
+        <v>0.6709248928978977</v>
       </c>
       <c r="M4" t="n">
-        <v>9.354838612460563</v>
+        <v>9.445984640065342</v>
       </c>
       <c r="N4" t="n">
-        <v>129.7703898208863</v>
+        <v>132.903034987814</v>
       </c>
       <c r="O4" t="n">
-        <v>11.39168072853547</v>
+        <v>11.52835786171708</v>
       </c>
       <c r="P4" t="n">
-        <v>367.0539294661594</v>
+        <v>366.8129271494827</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33313,28 +33435,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.16213331354567</v>
+        <v>2.186846221756686</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K5" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6555936282774948</v>
+        <v>0.6561946611679201</v>
       </c>
       <c r="M5" t="n">
-        <v>9.62926313790495</v>
+        <v>9.732725759118672</v>
       </c>
       <c r="N5" t="n">
-        <v>141.7121473699609</v>
+        <v>145.2796878949461</v>
       </c>
       <c r="O5" t="n">
-        <v>11.904291132611</v>
+        <v>12.05320239168604</v>
       </c>
       <c r="P5" t="n">
-        <v>361.4878756236217</v>
+        <v>361.2313953598175</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33391,28 +33513,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.361137781182133</v>
+        <v>2.382339591466537</v>
       </c>
       <c r="J6" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K6" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6592540149397061</v>
+        <v>0.6611346433057733</v>
       </c>
       <c r="M6" t="n">
-        <v>10.0347343719888</v>
+        <v>10.11658780080331</v>
       </c>
       <c r="N6" t="n">
-        <v>166.6798501732113</v>
+        <v>169.0795318937735</v>
       </c>
       <c r="O6" t="n">
-        <v>12.91045507227423</v>
+        <v>13.00305855919189</v>
       </c>
       <c r="P6" t="n">
-        <v>352.9167054834854</v>
+        <v>352.6971858595329</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33469,28 +33591,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.373858780846941</v>
+        <v>2.3960145960212</v>
       </c>
       <c r="J7" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6437080143775724</v>
+        <v>0.6457396402699526</v>
       </c>
       <c r="M7" t="n">
-        <v>10.32189706690228</v>
+        <v>10.39240938408937</v>
       </c>
       <c r="N7" t="n">
-        <v>181.3167009854253</v>
+        <v>183.9594030489124</v>
       </c>
       <c r="O7" t="n">
-        <v>13.46538900238034</v>
+        <v>13.56316346022978</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3049616942948</v>
+        <v>349.0759231509983</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33547,28 +33669,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.386437884397574</v>
+        <v>2.407820545759376</v>
       </c>
       <c r="J8" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6512480412050412</v>
+        <v>0.6532922980080327</v>
       </c>
       <c r="M8" t="n">
-        <v>10.24503790928235</v>
+        <v>10.30314988318725</v>
       </c>
       <c r="N8" t="n">
-        <v>176.7032403504528</v>
+        <v>179.1251331506693</v>
       </c>
       <c r="O8" t="n">
-        <v>13.29297710636909</v>
+        <v>13.38376378866085</v>
       </c>
       <c r="P8" t="n">
-        <v>344.010646731506</v>
+        <v>343.7893600440573</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33625,28 +33747,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.201806767456336</v>
+        <v>2.217347242670039</v>
       </c>
       <c r="J9" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K9" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6016937108490399</v>
+        <v>0.6049875377041704</v>
       </c>
       <c r="M9" t="n">
-        <v>10.61719323815436</v>
+        <v>10.63942302041844</v>
       </c>
       <c r="N9" t="n">
-        <v>185.9405515182179</v>
+        <v>186.8891686563609</v>
       </c>
       <c r="O9" t="n">
-        <v>13.63600203572212</v>
+        <v>13.67074133528833</v>
       </c>
       <c r="P9" t="n">
-        <v>344.2238417576104</v>
+        <v>344.0630013144246</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33703,28 +33825,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.175429874956017</v>
+        <v>2.188407540250662</v>
       </c>
       <c r="J10" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K10" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5827515493639726</v>
+        <v>0.5862661033724001</v>
       </c>
       <c r="M10" t="n">
-        <v>10.79483959136309</v>
+        <v>10.80952055748983</v>
       </c>
       <c r="N10" t="n">
-        <v>196.3249480062443</v>
+        <v>196.7592083375781</v>
       </c>
       <c r="O10" t="n">
-        <v>14.01160047982543</v>
+        <v>14.02708837705025</v>
       </c>
       <c r="P10" t="n">
-        <v>344.7270763238007</v>
+        <v>344.5927506021063</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33781,28 +33903,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.154652768579756</v>
+        <v>2.164979614202669</v>
       </c>
       <c r="J11" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K11" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5816777066477055</v>
+        <v>0.5851268515192757</v>
       </c>
       <c r="M11" t="n">
-        <v>10.71192103962273</v>
+        <v>10.72589838264498</v>
       </c>
       <c r="N11" t="n">
-        <v>193.1281810932357</v>
+        <v>193.1609642682693</v>
       </c>
       <c r="O11" t="n">
-        <v>13.89705656220898</v>
+        <v>13.898236012828</v>
       </c>
       <c r="P11" t="n">
-        <v>344.4553756827309</v>
+        <v>344.3484267743096</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33859,28 +33981,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.132471700810321</v>
+        <v>2.144337581700187</v>
       </c>
       <c r="J12" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K12" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5968925151424915</v>
+        <v>0.6003107042474636</v>
       </c>
       <c r="M12" t="n">
-        <v>10.5908619574654</v>
+        <v>10.60741741096023</v>
       </c>
       <c r="N12" t="n">
-        <v>177.6453150833953</v>
+        <v>177.9422949597167</v>
       </c>
       <c r="O12" t="n">
-        <v>13.3283650566525</v>
+        <v>13.33950130101259</v>
       </c>
       <c r="P12" t="n">
-        <v>348.1054102426301</v>
+        <v>347.982535159642</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33937,28 +34059,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.099872443780363</v>
+        <v>2.114858584538506</v>
       </c>
       <c r="J13" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K13" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5168543874440572</v>
+        <v>0.5209617868403087</v>
       </c>
       <c r="M13" t="n">
-        <v>11.67384053746182</v>
+        <v>11.71374974394536</v>
       </c>
       <c r="N13" t="n">
-        <v>238.4284843723082</v>
+        <v>239.0415512342943</v>
       </c>
       <c r="O13" t="n">
-        <v>15.44112963394545</v>
+        <v>15.46096863829347</v>
       </c>
       <c r="P13" t="n">
-        <v>344.9504027580656</v>
+        <v>344.7952419294471</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34019,28 +34141,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.770570945553339</v>
+        <v>1.793566686255021</v>
       </c>
       <c r="J14" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K14" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3929517438768442</v>
+        <v>0.398123965401076</v>
       </c>
       <c r="M14" t="n">
-        <v>12.99621055587328</v>
+        <v>13.02337672252767</v>
       </c>
       <c r="N14" t="n">
-        <v>281.0905147553332</v>
+        <v>283.6119340212559</v>
       </c>
       <c r="O14" t="n">
-        <v>16.76575422566289</v>
+        <v>16.84078187084127</v>
       </c>
       <c r="P14" t="n">
-        <v>344.1818843087246</v>
+        <v>343.9438363214636</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34082,7 +34204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O528"/>
+  <dimension ref="A1:O530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74685,6 +74807,160 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-36.90014375082986,174.44556026211416</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-36.899477218081984,174.44521972954928</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-36.89880624764716,174.44489048830766</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-36.898144532365414,174.44453765420624</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-36.89746615092559,174.44422726477632</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-36.89681099429726,174.4438576934183</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-36.89613430400567,174.4435429670041</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-36.895429906791165,174.44329881179164</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-36.89476261532393,174.44295683574157</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-36.89409368881406,174.44261871272016</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-36.89346768204837,174.44217309341437</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-36.89283695983515,174.44176685922332</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-36.89221550876477,174.4413468734048</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-36.90014636278285,174.44555360780458</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-36.899474685290414,174.4452261821646</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-36.898804941682265,174.4448938154123</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-36.89814674853725,174.4445320082516</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-36.897466230074265,174.44422706313665</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-36.89680909473869,174.44386253273555</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-36.89614150646749,174.4435246180657</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-36.895449456273184,174.44324900794345</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-36.89478892967028,174.44288941681245</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-36.894121057934264,174.44254806537214</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-36.89348609703966,174.44212547410334</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-36.89283404949413,174.44177408021602</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-36.89220682692967,174.44136755906968</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27454,6 +27454,57 @@
         <v>421.63</v>
       </c>
       <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>465.87</v>
+      </c>
+      <c r="C531" t="n">
+        <v>459.25</v>
+      </c>
+      <c r="D531" t="n">
+        <v>454.78</v>
+      </c>
+      <c r="E531" t="n">
+        <v>451.83</v>
+      </c>
+      <c r="F531" t="n">
+        <v>443.23</v>
+      </c>
+      <c r="G531" t="n">
+        <v>441.43</v>
+      </c>
+      <c r="H531" t="n">
+        <v>436.32</v>
+      </c>
+      <c r="I531" t="n">
+        <v>425.61</v>
+      </c>
+      <c r="J531" t="n">
+        <v>423.74</v>
+      </c>
+      <c r="K531" t="n">
+        <v>420.55</v>
+      </c>
+      <c r="L531" t="n">
+        <v>425.33</v>
+      </c>
+      <c r="M531" t="n">
+        <v>423.53</v>
+      </c>
+      <c r="N531" t="n">
+        <v>422.61</v>
+      </c>
+      <c r="O531" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27470,7 +27521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B556"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33033,6 +33084,16 @@
       </c>
       <c r="B556" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -33201,28 +33262,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.254538063962396</v>
+        <v>2.26526668010033</v>
       </c>
       <c r="J2" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6733853761454236</v>
+        <v>0.6740467268190855</v>
       </c>
       <c r="M2" t="n">
-        <v>9.330328015339695</v>
+        <v>9.372078169680988</v>
       </c>
       <c r="N2" t="n">
-        <v>142.5969145497725</v>
+        <v>143.8718018342087</v>
       </c>
       <c r="O2" t="n">
-        <v>11.94139500015691</v>
+        <v>11.99465722037144</v>
       </c>
       <c r="P2" t="n">
-        <v>376.4342834863386</v>
+        <v>376.3222659818873</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33279,28 +33340,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.303762029489229</v>
+        <v>2.314506724204997</v>
       </c>
       <c r="J3" t="n">
+        <v>530</v>
+      </c>
+      <c r="K3" t="n">
         <v>529</v>
       </c>
-      <c r="K3" t="n">
-        <v>528</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6922844677078065</v>
+        <v>0.6927729494753323</v>
       </c>
       <c r="M3" t="n">
-        <v>9.208723242100831</v>
+        <v>9.254849196888539</v>
       </c>
       <c r="N3" t="n">
-        <v>136.7818733640964</v>
+        <v>138.077551599682</v>
       </c>
       <c r="O3" t="n">
-        <v>11.69537829076496</v>
+        <v>11.75064047614776</v>
       </c>
       <c r="P3" t="n">
-        <v>368.3712593130381</v>
+        <v>368.2593386205223</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33357,28 +33418,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.161785720963864</v>
+        <v>2.172872754672812</v>
       </c>
       <c r="J4" t="n">
+        <v>530</v>
+      </c>
+      <c r="K4" t="n">
         <v>529</v>
       </c>
-      <c r="K4" t="n">
-        <v>528</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6709248928978977</v>
+        <v>0.6713974112207804</v>
       </c>
       <c r="M4" t="n">
-        <v>9.445984640065342</v>
+        <v>9.489843995015413</v>
       </c>
       <c r="N4" t="n">
-        <v>132.903034987814</v>
+        <v>134.3066636571417</v>
       </c>
       <c r="O4" t="n">
-        <v>11.52835786171708</v>
+        <v>11.58907518558499</v>
       </c>
       <c r="P4" t="n">
-        <v>366.8129271494827</v>
+        <v>366.6974405280871</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33435,28 +33496,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.186846221756686</v>
+        <v>2.19866283223152</v>
       </c>
       <c r="J5" t="n">
+        <v>530</v>
+      </c>
+      <c r="K5" t="n">
         <v>529</v>
       </c>
-      <c r="K5" t="n">
-        <v>528</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6561946611679201</v>
+        <v>0.6566920133296945</v>
       </c>
       <c r="M5" t="n">
-        <v>9.732725759118672</v>
+        <v>9.782063878619478</v>
       </c>
       <c r="N5" t="n">
-        <v>145.2796878949461</v>
+        <v>146.8848810875375</v>
       </c>
       <c r="O5" t="n">
-        <v>12.05320239168604</v>
+        <v>12.11960729922952</v>
       </c>
       <c r="P5" t="n">
-        <v>361.2313953598175</v>
+        <v>361.1083091984589</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33513,28 +33574,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.382339591466537</v>
+        <v>2.392139110619139</v>
       </c>
       <c r="J6" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K6" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6611346433057733</v>
+        <v>0.6622229091873577</v>
       </c>
       <c r="M6" t="n">
-        <v>10.11658780080331</v>
+        <v>10.15287258949301</v>
       </c>
       <c r="N6" t="n">
-        <v>169.0795318937735</v>
+        <v>170.0571953385156</v>
       </c>
       <c r="O6" t="n">
-        <v>13.00305855919189</v>
+        <v>13.040597967061</v>
       </c>
       <c r="P6" t="n">
-        <v>352.6971858595329</v>
+        <v>352.5953509536672</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33591,28 +33652,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3960145960212</v>
+        <v>2.406349707546949</v>
       </c>
       <c r="J7" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K7" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6457396402699526</v>
+        <v>0.6468887235560337</v>
       </c>
       <c r="M7" t="n">
-        <v>10.39240938408937</v>
+        <v>10.42387140334854</v>
       </c>
       <c r="N7" t="n">
-        <v>183.9594030489124</v>
+        <v>185.0626287921427</v>
       </c>
       <c r="O7" t="n">
-        <v>13.56316346022978</v>
+        <v>13.60377259410575</v>
       </c>
       <c r="P7" t="n">
-        <v>349.0759231509983</v>
+        <v>348.9686858252344</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33669,28 +33730,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.407820545759376</v>
+        <v>2.418107117559273</v>
       </c>
       <c r="J8" t="n">
+        <v>530</v>
+      </c>
+      <c r="K8" t="n">
         <v>529</v>
       </c>
-      <c r="K8" t="n">
-        <v>528</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6532922980080327</v>
+        <v>0.6543901998104182</v>
       </c>
       <c r="M8" t="n">
-        <v>10.30314988318725</v>
+        <v>10.33007857293326</v>
       </c>
       <c r="N8" t="n">
-        <v>179.1251331506693</v>
+        <v>180.2185855328765</v>
       </c>
       <c r="O8" t="n">
-        <v>13.38376378866085</v>
+        <v>13.42455159522568</v>
       </c>
       <c r="P8" t="n">
-        <v>343.7893600440573</v>
+        <v>343.6825168160921</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33747,28 +33808,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.217347242670039</v>
+        <v>2.225456798613108</v>
       </c>
       <c r="J9" t="n">
+        <v>530</v>
+      </c>
+      <c r="K9" t="n">
         <v>529</v>
       </c>
-      <c r="K9" t="n">
-        <v>528</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.6049875377041704</v>
+        <v>0.6066218964304071</v>
       </c>
       <c r="M9" t="n">
-        <v>10.63942302041844</v>
+        <v>10.65190138649294</v>
       </c>
       <c r="N9" t="n">
-        <v>186.8891686563609</v>
+        <v>187.425932254836</v>
       </c>
       <c r="O9" t="n">
-        <v>13.67074133528833</v>
+        <v>13.69035909882703</v>
       </c>
       <c r="P9" t="n">
-        <v>344.0630013144246</v>
+        <v>343.9787700320132</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33825,28 +33886,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.188407540250662</v>
+        <v>2.195912567840392</v>
       </c>
       <c r="J10" t="n">
+        <v>530</v>
+      </c>
+      <c r="K10" t="n">
         <v>529</v>
       </c>
-      <c r="K10" t="n">
-        <v>528</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5862661033724001</v>
+        <v>0.58802979029888</v>
       </c>
       <c r="M10" t="n">
-        <v>10.80952055748983</v>
+        <v>10.82136348998064</v>
       </c>
       <c r="N10" t="n">
-        <v>196.7592083375781</v>
+        <v>197.1495619456181</v>
       </c>
       <c r="O10" t="n">
-        <v>14.02708837705025</v>
+        <v>14.04099576047291</v>
       </c>
       <c r="P10" t="n">
-        <v>344.5927506021063</v>
+        <v>344.51479835628</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33903,28 +33964,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.164979614202669</v>
+        <v>2.171623512675595</v>
       </c>
       <c r="J11" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K11" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5851268515192757</v>
+        <v>0.5869092632156696</v>
       </c>
       <c r="M11" t="n">
-        <v>10.72589838264498</v>
+        <v>10.7413067919565</v>
       </c>
       <c r="N11" t="n">
-        <v>193.1609642682693</v>
+        <v>193.3925418336179</v>
       </c>
       <c r="O11" t="n">
-        <v>13.898236012828</v>
+        <v>13.90656470281636</v>
       </c>
       <c r="P11" t="n">
-        <v>344.3484267743096</v>
+        <v>344.2793845320286</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33981,28 +34042,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.144337581700187</v>
+        <v>2.15161507567863</v>
       </c>
       <c r="J12" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K12" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6003107042474636</v>
+        <v>0.6020042635327759</v>
       </c>
       <c r="M12" t="n">
-        <v>10.60741741096023</v>
+        <v>10.62254686241335</v>
       </c>
       <c r="N12" t="n">
-        <v>177.9422949597167</v>
+        <v>178.3216888498756</v>
       </c>
       <c r="O12" t="n">
-        <v>13.33950130101259</v>
+        <v>13.35371442145876</v>
       </c>
       <c r="P12" t="n">
-        <v>347.982535159642</v>
+        <v>347.9069087025994</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34059,28 +34120,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.114858584538506</v>
+        <v>2.122950079812038</v>
       </c>
       <c r="J13" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K13" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5209617868403087</v>
+        <v>0.5230189430027155</v>
       </c>
       <c r="M13" t="n">
-        <v>11.71374974394536</v>
+        <v>11.73737991263689</v>
       </c>
       <c r="N13" t="n">
-        <v>239.0415512342943</v>
+        <v>239.4745885999127</v>
       </c>
       <c r="O13" t="n">
-        <v>15.46096863829347</v>
+        <v>15.47496651369277</v>
       </c>
       <c r="P13" t="n">
-        <v>344.7952419294471</v>
+        <v>344.7111565119219</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34141,28 +34202,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.793566686255021</v>
+        <v>1.804859962917726</v>
       </c>
       <c r="J14" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K14" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L14" t="n">
-        <v>0.398123965401076</v>
+        <v>0.4007021943839751</v>
       </c>
       <c r="M14" t="n">
-        <v>13.02337672252767</v>
+        <v>13.0362404979217</v>
       </c>
       <c r="N14" t="n">
-        <v>283.6119340212559</v>
+        <v>284.8059633840268</v>
       </c>
       <c r="O14" t="n">
-        <v>16.84078187084127</v>
+        <v>16.87619516905475</v>
       </c>
       <c r="P14" t="n">
-        <v>343.9438363214636</v>
+        <v>343.8264935061075</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34204,7 +34265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74961,6 +75022,83 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-36.90014268230353,174.44556298433156</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-36.8994681554356,174.44524281781136</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-36.89880213187872,174.4449009737279</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-36.8981421183208,174.4445438042636</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-36.89745973988115,174.44424359758779</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-36.89680426669312,174.44387483266576</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-36.89613568909469,174.4435394383624</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-36.89544494485607,174.4432605011415</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-36.89478802363802,174.44289173812365</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-36.8941242686152,174.44253977769705</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-36.89349243085404,174.44210909548138</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-36.892843629365025,174.44175031111294</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-36.89221091741012,174.44135781293969</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
